--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.1%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.5%</t>
+          <t>-617.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.7%</t>
+          <t>-277.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-148.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-244.5%</t>
+          <t>-265.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.1%</t>
+          <t>-189.6%</t>
         </is>
       </c>
     </row>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -45395,10 +45395,10 @@
         <v>0.05593786303537174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.592190558793033</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.198727226007749</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>0.168444123732463</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.592190558793033</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.211633567231408</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>-0.001767801775997668</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.697780548566137</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.020303643768326</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>0.03928257925364997</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.697780548566137</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.068847985645413</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>-0.02142032687147788</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.67745963265758</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>1.96116161250238</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>-0.02327105307243826</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.660301482526285</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>1.962742516327678</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>-0.01281230245925524</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.660301482526285</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>1.955781904232585</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>0.09850940930343111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.660301482526285</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>1.970244258613728</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>0.1363451846116348</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.660301482526285</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>1.964776379072923</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>0.1831597325490639</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.537010347709155</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.036249153973778</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>0.1993203903477667</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.515861148805711</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.056639651553169</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.2926072754881948</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.515861148805711</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.05242035990022</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.353490400495359</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.468202906827123</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.083139619007389</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.446172633058691</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.468202906827123</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.075881693991091</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.5201285935663122</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.468202906827123</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.07948081751174</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>0.6020346848298517</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.29675644380466</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.195676201379771</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>0.6910683623136777</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-1.071723444135837</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.329716478797362</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>0.7212174602615686</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-1.008087701901903</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.37259272519204</v>
       </c>
     </row>
     <row r="1924">
@@ -45809,10 +45809,10 @@
         <v>0.7396117355277236</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-1.008087701901903</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.353786983975836</v>
       </c>
     </row>
     <row r="1925">
@@ -45832,10 +45832,10 @@
         <v>0.8375270108745454</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.7676572050970427</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.499788358683629</v>
       </c>
     </row>
     <row r="1926">
@@ -45855,10 +45855,10 @@
         <v>0.8703533519778435</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.7676572050970427</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.503717672518449</v>
       </c>
     </row>
     <row r="1927">
@@ -45878,10 +45878,10 @@
         <v>0.8922312648077386</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.7123209460951039</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.537598011836953</v>
       </c>
     </row>
     <row r="1928">
@@ -45901,10 +45901,10 @@
         <v>0.9327512902196227</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.7123209460951039</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.534596083056946</v>
       </c>
     </row>
     <row r="1929">
@@ -45924,10 +45924,10 @@
         <v>1.022338646445041</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5711011010271236</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.620907027108349</v>
       </c>
     </row>
     <row r="1930">
@@ -45947,10 +45947,10 @@
         <v>1.091379904872176</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5711011010271236</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.636801209910172</v>
       </c>
     </row>
     <row r="1931">
@@ -45970,10 +45970,10 @@
         <v>1.156331790720225</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.4115859975077537</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.733656116462096</v>
       </c>
     </row>
     <row r="1932">
@@ -45993,10 +45993,10 @@
         <v>1.22428875132156</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.2669138524080163</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.830547506083378</v>
       </c>
     </row>
     <row r="1933">
@@ -46016,10 +46016,10 @@
         <v>1.186376311779909</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.3267886797657084</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.780660101070189</v>
       </c>
     </row>
     <row r="1934">
@@ -46039,10 +46039,10 @@
         <v>1.243496604214079</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.3267886797657084</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.803060594392755</v>
       </c>
     </row>
     <row r="1935">
@@ -46062,10 +46062,10 @@
         <v>1.242581123002769</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.3292583862275146</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.801651171889083</v>
       </c>
     </row>
     <row r="1936">
@@ -46085,10 +46085,10 @@
         <v>1.226239970947866</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.3199826871912996</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.818223513785514</v>
       </c>
     </row>
     <row r="1937">
@@ -46108,10 +46108,10 @@
         <v>1.173261407213304</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.3199826871912996</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.808660222417406</v>
       </c>
     </row>
     <row r="1938">
@@ -46131,10 +46131,10 @@
         <v>0.9855737085222089</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.3199826871912996</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.633369787457792</v>
       </c>
     </row>
     <row r="1939">
@@ -46154,10 +46154,10 @@
         <v>1.060330644430984</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.3199826871912996</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.63793701944958</v>
       </c>
     </row>
     <row r="1940">
@@ -46177,10 +46177,10 @@
         <v>0.9916981721356917</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.3199826871912996</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.613679048210787</v>
       </c>
     </row>
     <row r="1941">
@@ -46200,10 +46200,10 @@
         <v>0.9136189263383039</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.523009264734533</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.494994486904753</v>
       </c>
     </row>
     <row r="1942">
@@ -46223,10 +46223,10 @@
         <v>0.9869615523445534</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.523009264734533</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.505166873336885</v>
       </c>
     </row>
     <row r="1943">
@@ -46246,10 +46246,10 @@
         <v>1.016405208128965</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.523009264734533</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.500113143910745</v>
       </c>
     </row>
     <row r="1944">
@@ -46269,10 +46269,10 @@
         <v>0.9900582558138984</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.5638194277437638</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.569256935152479</v>
+        <v>2.467402821549732</v>
       </c>
     </row>
     <row r="1945">
@@ -46292,10 +46292,10 @@
         <v>0.9789968869660797</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.5638194277437638</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569808808185581</v>
+        <v>2.467954694582834</v>
       </c>
     </row>
     <row r="1946">
@@ -46315,10 +46315,10 @@
         <v>0.9453937714377891</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3012520902883266</v>
+        <v>-0.4710089462929045</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554767788947462</v>
+        <v>2.452913675344715</v>
       </c>
     </row>
     <row r="1947">
@@ -46338,10 +46338,10 @@
         <v>0.9666924682508018</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2526890380672964</v>
+        <v>-0.4224458940718743</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.585779096204681</v>
+        <v>2.483924982601934</v>
       </c>
     </row>
     <row r="1948">
@@ -46361,10 +46361,10 @@
         <v>1.006836664057025</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.3097746758356241</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.648457535658154</v>
+        <v>2.546603422055407</v>
       </c>
     </row>
     <row r="1949">
@@ -46384,10 +46384,10 @@
         <v>1.057278760360761</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.3097746758356241</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.653948831488821</v>
+        <v>2.552094717886074</v>
       </c>
     </row>
     <row r="1950">
@@ -46407,10 +46407,10 @@
         <v>0.9894821345746081</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3382523887177767</v>
+        <v>-0.5080092447223546</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.546505291925322</v>
+        <v>2.444651178322575</v>
       </c>
     </row>
     <row r="1951">
@@ -46430,10 +46430,10 @@
         <v>0.7946373421651498</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.5265801292495284</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.373718481209671</v>
+        <v>2.271864367606924</v>
       </c>
     </row>
     <row r="1952">
@@ -46453,10 +46453,10 @@
         <v>0.8639602003615603</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.5265801292495284</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.493868141928877</v>
+        <v>2.39201402832613</v>
       </c>
     </row>
     <row r="1953">
@@ -46476,10 +46476,10 @@
         <v>0.8438337932714419</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.5265801292495284</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.5083811680312</v>
+        <v>2.406527054428453</v>
       </c>
     </row>
     <row r="1954">
@@ -46499,10 +46499,10 @@
         <v>0.8566066996370711</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.4881964666913772</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.528830806908459</v>
+        <v>2.426976693305712</v>
       </c>
     </row>
     <row r="1955">
@@ -46522,10 +46522,10 @@
         <v>0.9241822604964396</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.4881964666913772</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.525559835753761</v>
+        <v>2.423705722151014</v>
       </c>
     </row>
     <row r="1956">
@@ -46545,10 +46545,10 @@
         <v>0.9367465018488701</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3229097359021127</v>
+        <v>-0.4926665919066905</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.523561152386486</v>
+        <v>2.421707038783739</v>
       </c>
     </row>
     <row r="1957">
@@ -46568,10 +46568,10 @@
         <v>1.002283645650792</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.166132977731394</v>
+        <v>-0.3358898337359719</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.611414182595332</v>
+        <v>2.509560068992585</v>
       </c>
     </row>
     <row r="1958">
@@ -46591,10 +46591,10 @@
         <v>0.9650854155741388</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1964818730459986</v>
+        <v>-0.3662387290505765</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.574012300738159</v>
+        <v>2.472158187135412</v>
       </c>
     </row>
     <row r="1959">
@@ -46614,10 +46614,10 @@
         <v>0.8639751738041106</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3908449110889472</v>
+        <v>-0.560601767093525</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.463086040251335</v>
+        <v>2.361231926648588</v>
       </c>
     </row>
     <row r="1960">
@@ -46637,10 +46637,10 @@
         <v>0.8226999831257431</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.6290105806388443</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.421244674020645</v>
+        <v>2.319390560417898</v>
       </c>
     </row>
     <row r="1961">
@@ -46660,10 +46660,10 @@
         <v>0.8332901791483687</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.6290105806388443</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.418844635574962</v>
+        <v>2.316990521972215</v>
       </c>
     </row>
     <row r="1962">
@@ -46683,10 +46683,10 @@
         <v>0.8374301494395324</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6871941919700388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.278605074381743</v>
       </c>
     </row>
     <row r="1963">
@@ -46706,10 +46706,10 @@
         <v>1.002561365917966</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6871941919700388</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.456186943320424</v>
       </c>
     </row>
     <row r="1964">
@@ -46729,10 +46729,10 @@
         <v>0.9824665426637824</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.6522473319611667</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.477988388311881</v>
       </c>
     </row>
     <row r="1965">
@@ -46752,10 +46752,10 @@
         <v>0.930745910690741</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.6522473319611667</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.483996918708807</v>
       </c>
     </row>
     <row r="1966">
@@ -46775,10 +46775,10 @@
         <v>1.068995746576764</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4844399747262835</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.663833980841758</v>
       </c>
     </row>
     <row r="1967">
@@ -46798,10 +46798,10 @@
         <v>1.030983495095756</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4844399747262835</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.666627602373239</v>
       </c>
     </row>
     <row r="1968">
@@ -46821,10 +46821,10 @@
         <v>1.086289581125052</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.3478306306321911</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.749255557221353</v>
       </c>
     </row>
     <row r="1969">
@@ -46844,10 +46844,10 @@
         <v>1.028263924736102</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4905959634548415</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.662676834267873</v>
       </c>
     </row>
     <row r="1970">
@@ -46867,10 +46867,10 @@
         <v>1.119518678043372</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4905959634548415</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.729012388064694</v>
       </c>
     </row>
     <row r="1971">
@@ -46890,10 +46890,10 @@
         <v>0.908815629498833</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.2925777712856871</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.556404175755585</v>
       </c>
     </row>
     <row r="1972">
@@ -46913,10 +46913,10 @@
         <v>1.003062134478045</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.2326870896430936</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.662628817063316</v>
       </c>
     </row>
     <row r="1973">
@@ -46936,10 +46936,10 @@
         <v>0.9785936527440993</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.2485763677760738</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.667722986299572</v>
       </c>
     </row>
     <row r="1974">
@@ -46959,10 +46959,10 @@
         <v>0.9065945295195994</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.4249141278990032</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.560456311050486</v>
       </c>
     </row>
     <row r="1975">
@@ -46982,10 +46982,10 @@
         <v>0.9053618964240171</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.4249141278990032</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.558947929090414</v>
       </c>
     </row>
     <row r="1976">
@@ -47005,10 +47005,10 @@
         <v>0.9025963778376163</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.4314850929535961</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.554868217493095</v>
       </c>
     </row>
     <row r="1977">
@@ -47028,10 +47028,10 @@
         <v>0.9057779659555252</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.4314850929535961</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.554868217493095</v>
       </c>
     </row>
     <row r="1978">
@@ -47051,10 +47051,10 @@
         <v>0.9163090735165644</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.4211117166205088</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.567474000320752</v>
       </c>
     </row>
     <row r="1979">
@@ -47074,10 +47074,10 @@
         <v>0.9722751708090078</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1236705508216345</v>
+        <v>-0.2934274068262124</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.750831073174801</v>
+        <v>2.648976959572054</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.781344436736541</v>
+        <v>3.499618847980526</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.689535933863135</v>
+        <v>-4.559069279500522</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9356172782846521</v>
+        <v>0.9878039400296974</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2046255946682844</v>
+        <v>-0.4129920161376368</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.689012719342683</v>
+        <v>2.563992866461072</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-657.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.9%</t>
+          <t>440.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.5%</t>
+          <t>-622.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-263.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-279.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.9%</t>
+          <t>-139.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.3%</t>
+          <t>-244.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-189.6%</t>
+          <t>-177.2%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.0129598482530679</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.162338771597964</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.01799743898065442</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.162931248074337</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.1446286409839841</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.076627197712219</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.2103960310333962</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.051337850822924</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4962344954519427</v>
+        <v>-0.4156407080906408</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.927630497043261</v>
+        <v>2.959868011987782</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5780063958796944</v>
+        <v>-0.4974126085183925</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.885004462827399</v>
+        <v>2.917241977771919</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.5646217163902701</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.895123651456871</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-0.772187500781882</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.809922133819466</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.189941524328719</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.640747415905794</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.393230993650522</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.559297844775995</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.601235052003599</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.48098836598869</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-1.812647472891574</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.391504853971488</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.151805850480097</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.248925802242528</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.360296631931781</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.185867779400622</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.607497816697003</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>2.095086055903102</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.0998828447211</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.899238436737196</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.485063235651172</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.74370881917803</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-3.828746008877835</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.608004833341981</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.035257785764856</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.52150618124343</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.291098871543549</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.420942673632212</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.722904664693337</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.234553243839702</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-4.957598658825889</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.128960421188772</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.293261306056341</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9932759539525557</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.656887550956655</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8543130162266719</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.022014933595401</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.7075165781770045</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.430603710776079</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5428426113194926</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.707179811091912</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.4273976036646201</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.123571685378909</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2588349045586984</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.440183627919557</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.1424488182111183</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-7.786058449904367</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>0.0001984545628896939</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-7.949638328088751</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.06682857665586317</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.246299669898949</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.1817141374507343</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.531924638034567</v>
+        <v>-8.451330850673266</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2999904292393847</v>
+        <v>-0.2677529142948636</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.914926026777199</v>
+        <v>-8.834332239415897</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4532930860580211</v>
+        <v>-0.4210555711135004</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.096795817762233</v>
+        <v>-9.016202030400931</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5234694864806047</v>
+        <v>-0.491231971536084</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.456326140266235</v>
+        <v>-9.375732352904933</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.661931312184155</v>
+        <v>-0.6296937972396344</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.506675203720457</v>
+        <v>-9.426081416359155</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6741549176086665</v>
+        <v>-0.6419174026641459</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.604294481141853</v>
+        <v>-9.523700693780551</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.710160877955456</v>
+        <v>-0.6779233630109354</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.751820569147496</v>
+        <v>-9.671226781786194</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.766277756836141</v>
+        <v>-0.7340402418916203</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.95607874447736</v>
+        <v>-9.875484957116058</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8424678298494443</v>
+        <v>-0.8102303149049233</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09788851868415</v>
+        <v>-10.01729473132285</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8947091850477231</v>
+        <v>-0.8624716701032029</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0244186870167</v>
+        <v>-9.943824899655397</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8499495508873229</v>
+        <v>-0.8177120359428018</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19954310440324</v>
+        <v>-10.11894931704194</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9054440970944233</v>
+        <v>-0.8732065821499022</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43399519841773</v>
+        <v>-10.35340141105643</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.006444099601815</v>
+        <v>-0.9742065846572943</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.64120525559367</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.096000313246166</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390588</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.69399141119399</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.115998985647741</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297402</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-10.92602033093026</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.20611682491313</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-10.87400481696144</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.181320283639204</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-11.01567665868556</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.239464247227594</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-10.96608581426073</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.204574499292788</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.76693370702363</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.137964790044631</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.54108855430422</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.038047655920658</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.41650989796663</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-0.9870770488295633</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.46940518601092</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-1.00560138988517</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.18549645508217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.8863041932750342</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.11413006247252</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.8674948986250399</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-9.850293195268449</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.7718436330563199</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.583051394400051</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.6667814732083346</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.485144355723561</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.6279189727111993</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.461190814747603</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.6176690501753224</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.197130876424806</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.5253053910079557</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.490051252919969</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.2452605752663217</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.449866954553778</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.2288432320320042</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.369797159015974</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.1974484925961253</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.136315936786374</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.09613157486643331</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-7.986649545778859</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.03915722877638661</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-7.854374072147973</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>0.009120447422995337</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.66377439747482</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>0.08817537797989283</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.592190558793033</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.198727226007749</v>
+        <v>2.300581339610495</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.414774598791239</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.2006816386769841</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.592190558793033</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.211633567231408</v>
+        <v>2.313487680834154</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.520364588564344</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>0.03046971316852343</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.697780548566137</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.020303643768326</v>
+        <v>2.122157757371073</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.539099490682941</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>0.07152009419817107</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.697780548566137</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.068847985645413</v>
+        <v>2.170702099248159</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.391159449275341</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>0.01081718807304322</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.67745963265758</v>
+        <v>-1.507702776653002</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.96116161250238</v>
+        <v>2.063015726105126</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.374001299144047</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>0.008966461872082832</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.660301482526285</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.962742516327678</v>
+        <v>2.064596629930425</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.330452892373357</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>0.01942521248526585</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.660301482526285</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.955781904232585</v>
+        <v>2.057636017835332</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.088304498919499</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.1307469242479522</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.660301482526285</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.970244258613728</v>
+        <v>2.072098372216475</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.06063914915828</v>
+        <v>-6.980045361796977</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1363451846116348</v>
+        <v>0.1685826995561559</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.660301482526285</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.964776379072923</v>
+        <v>2.06663049267567</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.937348014341149</v>
+        <v>-6.856754226979846</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1831597325490639</v>
+        <v>0.215397247493585</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.537010347709155</v>
+        <v>-1.367253491704577</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.036249153973778</v>
+        <v>2.138103267576525</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.916198815437705</v>
+        <v>-6.835605028076403</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1993203903477667</v>
+        <v>0.2315579052922878</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.515861148805711</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.056639651553169</v>
+        <v>2.158493765155916</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.672433373454261</v>
+        <v>-6.591839586092958</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2926072754881948</v>
+        <v>0.3248447904327159</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.515861148805711</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.05242035990022</v>
+        <v>2.154274473502967</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.525536345736391</v>
+        <v>-6.444942558375088</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.353490400495359</v>
+        <v>0.3857279154398805</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.468202906827123</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.083139619007389</v>
+        <v>2.184993732610136</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.275685951787317</v>
+        <v>-6.195092164426013</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.446172633058691</v>
+        <v>0.4784101480032121</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.468202906827123</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.075881693991091</v>
+        <v>2.177735807593838</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.099793859319885</v>
+        <v>-6.019200071958581</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5201285935663122</v>
+        <v>0.5523661085108338</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.468202906827123</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.07948081751174</v>
+        <v>2.181334931114487</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.928347396297421</v>
+        <v>-5.847753608936118</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6020346848298517</v>
+        <v>0.6342721997743732</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.29675644380466</v>
+        <v>-1.126999587800082</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.195676201379771</v>
+        <v>2.297530314982518</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.703314396628598</v>
+        <v>-5.622720609267295</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6910683623136777</v>
+        <v>0.7233058772581993</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.071723444135837</v>
+        <v>-0.9019665881312596</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329716478797362</v>
+        <v>2.431570592400109</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.639678654394664</v>
+        <v>-5.55908486703336</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7212174602615686</v>
+        <v>0.7534549752060902</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.008087701901903</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37259272519204</v>
+        <v>2.474446838794787</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.546678613188766</v>
+        <v>-5.466084825827462</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7396117355277236</v>
+        <v>0.7718492504722452</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.008087701901903</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353786983975836</v>
+        <v>2.455641097578583</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.306248116383905</v>
+        <v>-5.225654329022602</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8375270108745454</v>
+        <v>0.8697645258190665</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7676572050970427</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499788358683629</v>
+        <v>2.601642472286376</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.234005548212711</v>
+        <v>-5.153411760851407</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8703533519778435</v>
+        <v>0.9025908669223646</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7676572050970427</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503717672518449</v>
+        <v>2.605571786121196</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.181007225931323</v>
+        <v>-5.100413438570019</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8922312648077386</v>
+        <v>0.9244687797522597</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7123209460951039</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.537598011836953</v>
+        <v>2.639452125439699</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.072202340451596</v>
+        <v>-4.991608553090292</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9327512902196227</v>
+        <v>0.9649888051641442</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7123209460951039</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.534596083056946</v>
+        <v>2.636450196659693</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.852181542414585</v>
+        <v>-4.771587755053281</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.022338646445041</v>
+        <v>1.054576161389563</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5711011010271236</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620907027108349</v>
+        <v>2.722761140711095</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.719313853351307</v>
+        <v>-4.638720065990004</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.091379904872176</v>
+        <v>1.123617419816697</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5711011010271236</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636801209910172</v>
+        <v>2.738655323512919</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.559798749831938</v>
+        <v>-4.479204962470634</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.156331790720225</v>
+        <v>1.188569305664747</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4115859975077537</v>
+        <v>-0.2418291415031758</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.733656116462096</v>
+        <v>2.835510230064842</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.4151266047322</v>
+        <v>-4.334532817370897</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22428875132156</v>
+        <v>1.256526266266082</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2669138524080163</v>
+        <v>-0.09715699640343839</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.830547506083378</v>
+        <v>2.932401619686125</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.475001432089893</v>
+        <v>-4.394407644728589</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.186376311779909</v>
+        <v>1.21861382672443</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3267886797657084</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.780660101070189</v>
+        <v>2.882514214672935</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.388201934310883</v>
+        <v>-4.30760814694958</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.243496604214079</v>
+        <v>1.2757341191586</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3267886797657084</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.803060594392755</v>
+        <v>2.904914707995502</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.390671640772689</v>
+        <v>-4.310077853411386</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.242581123002769</v>
+        <v>1.27481863794729</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3292583862275146</v>
+        <v>-0.1595015302229367</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.801651171889083</v>
+        <v>2.90350528549183</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.4590418270967</v>
+        <v>-4.378448039735396</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.226239970947866</v>
+        <v>1.258477485892388</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3199826871912996</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.818223513785514</v>
+        <v>2.920077627388261</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.567580008012833</v>
+        <v>-4.48698622065153</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.173261407213304</v>
+        <v>1.205498922157826</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3199826871912996</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.808660222417406</v>
+        <v>2.910514336020152</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.598573167341539</v>
+        <v>-4.517979379980235</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9855737085222089</v>
+        <v>1.01781122346673</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3199826871912996</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.633369787457792</v>
+        <v>2.735223901060539</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.42309890754907</v>
+        <v>-4.342505120187766</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.060330644430984</v>
+        <v>1.092568159375506</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3199826871912996</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.63793701944958</v>
+        <v>2.739791133052327</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.534035160190319</v>
+        <v>-4.453441372829015</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9916981721356917</v>
+        <v>1.023935687080213</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3199826871912996</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.613679048210787</v>
+        <v>2.715533161813534</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.737061737733552</v>
+        <v>-4.656467950372249</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9136189263383039</v>
+        <v>0.9458564412828254</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.523009264734533</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.494994486904753</v>
+        <v>2.596848600507499</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.579136138798259</v>
+        <v>-4.498542351436956</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9869615523445534</v>
+        <v>1.019199067289075</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.523009264734533</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.505166873336885</v>
+        <v>2.607020986939632</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.492892675771881</v>
+        <v>-4.412298888410578</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.016405208128965</v>
+        <v>1.048642723073486</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.523009264734533</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.500113143910745</v>
+        <v>2.601967257513492</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.538199495170861</v>
+        <v>-4.457605707809558</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9900582558138984</v>
+        <v>1.02229577075842</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5638194277437638</v>
+        <v>-0.3940625717391859</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.467402821549732</v>
+        <v>2.569256935152479</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.567232599873162</v>
+        <v>-4.486638812511859</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9789968869660797</v>
+        <v>1.011234401910601</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5638194277437638</v>
+        <v>-0.3940625717391859</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.467954694582834</v>
+        <v>2.569808808185581</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.474422118422303</v>
+        <v>-4.393828331060999</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9453937714377891</v>
+        <v>0.9776312863823104</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4710089462929045</v>
+        <v>-0.3012520902883266</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.452913675344715</v>
+        <v>2.554767788947462</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.425859066201273</v>
+        <v>-4.345265278839969</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9666924682508018</v>
+        <v>0.9989299831953233</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4224458940718743</v>
+        <v>-0.2526890380672964</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.483924982601934</v>
+        <v>2.585779096204681</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.313187847965023</v>
+        <v>-4.232594060603719</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.006836664057025</v>
+        <v>1.039074179001546</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3097746758356241</v>
+        <v>-0.1400178198310462</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.546603422055407</v>
+        <v>2.648457535658154</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.20081084678235</v>
+        <v>-4.120217059421046</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.057278760360761</v>
+        <v>1.089516275305283</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3097746758356241</v>
+        <v>-0.1400178198310462</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.552094717886074</v>
+        <v>2.653948831488821</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.399045415669081</v>
+        <v>-4.318451628307777</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9894821345746081</v>
+        <v>1.02171964951913</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5080092447223546</v>
+        <v>-0.3382523887177767</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.444651178322575</v>
+        <v>2.546505291925322</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.48204669669436</v>
+        <v>-4.401452909333056</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7946373421651498</v>
+        <v>0.8268748571096713</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5265801292495284</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.271864367606924</v>
+        <v>2.373718481209671</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.609113703001348</v>
+        <v>-4.528519915640044</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8639602003615603</v>
+        <v>0.8961977153060816</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5265801292495284</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.39201402832613</v>
+        <v>2.493868141928877</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.69571228598245</v>
+        <v>-4.615118498621147</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8438337932714419</v>
+        <v>0.8760713082159635</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5265801292495284</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.406527054428453</v>
+        <v>2.5083811680312</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.657328623424299</v>
+        <v>-4.576734836062996</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8566066996370711</v>
+        <v>0.8888442145815927</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4881964666913772</v>
+        <v>-0.3184396106867993</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.426976693305712</v>
+        <v>2.528830806908459</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.480212293389133</v>
+        <v>-4.39961850602783</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9241822604964396</v>
+        <v>0.9564197754409609</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4881964666913772</v>
+        <v>-0.3184396106867993</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.423705722151014</v>
+        <v>2.525559835753761</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45051016941284</v>
+        <v>-4.369916382051536</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9367465018488701</v>
+        <v>0.9689840167933914</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4926665919066905</v>
+        <v>-0.3229097359021127</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.421707038783739</v>
+        <v>2.523561152386486</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.271134748174072</v>
+        <v>-4.190540960812768</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.002283645650792</v>
+        <v>1.034521160595313</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3358898337359719</v>
+        <v>-0.166132977731394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.509560068992585</v>
+        <v>2.611414182595332</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.316148961694678</v>
+        <v>-4.235555174333374</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9650854155741388</v>
+        <v>0.9973229305186604</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3662387290505765</v>
+        <v>-0.1964818730459986</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.472158187135412</v>
+        <v>2.574012300738159</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.583153471967113</v>
+        <v>-4.502559684605809</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8639751738041106</v>
+        <v>0.8962126887486321</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.560601767093525</v>
+        <v>-0.3908449110889472</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.361231926648588</v>
+        <v>2.463086040251335</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.684351253404285</v>
+        <v>-4.603757466042982</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8226999831257431</v>
+        <v>0.8549374980702644</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6290105806388443</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.319390560417898</v>
+        <v>2.421244674020645</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.651875667233513</v>
+        <v>-4.57128187987221</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8332901791483687</v>
+        <v>0.86552769409289</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6290105806388443</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.316990521972215</v>
+        <v>2.418844635574962</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.632837539526216</v>
+        <v>-4.552243752164912</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8374301494395324</v>
+        <v>0.869667664384054</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6871941919700388</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.278605074381743</v>
+        <v>2.38045918798449</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.663964170676834</v>
+        <v>-4.583370383315531</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.002561365917966</v>
+        <v>1.034798880862487</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6871941919700388</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.456186943320424</v>
+        <v>2.55804105692317</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.716284551277626</v>
+        <v>-4.635690763916323</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9824665426637824</v>
+        <v>1.014704057608304</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6522473319611667</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.477988388311881</v>
+        <v>2.579842501914627</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.860607457202545</v>
+        <v>-4.780013669841241</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.930745910690741</v>
+        <v>0.9629834256352623</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6522473319611667</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.483996918708807</v>
+        <v>2.585851032311553</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.712864486967542</v>
+        <v>-4.632270699606239</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.068995746576764</v>
+        <v>1.101233261521285</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4844399747262835</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.663833980841758</v>
+        <v>2.765688094444505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.814879169498764</v>
+        <v>-4.73428538213746</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.030983495095756</v>
+        <v>1.063221010040278</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4844399747262835</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.666627602373239</v>
+        <v>2.768481715975986</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.678269825404671</v>
+        <v>-4.597676038043367</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.086289581125052</v>
+        <v>1.118527096069573</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3478306306321911</v>
+        <v>-0.1780737746276131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.749255557221353</v>
+        <v>2.8511096708241</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.821035158227321</v>
+        <v>-4.740441370866018</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.028263924736102</v>
+        <v>1.060501439680623</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4905959634548415</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.662676834267873</v>
+        <v>2.76453094787062</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.758737159451199</v>
+        <v>-4.678143372089895</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.119518678043372</v>
+        <v>1.151756192987893</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4905959634548415</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.729012388064694</v>
+        <v>2.830866501667441</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.556946961786041</v>
+        <v>-4.476353174424737</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.908815629498833</v>
+        <v>0.9410531444433543</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2925777712856871</v>
+        <v>-0.1228209152811092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.556404175755585</v>
+        <v>2.658258289358332</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.497056280143448</v>
+        <v>-4.416462492782144</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.003062134478045</v>
+        <v>1.035299649422567</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2326870896430936</v>
+        <v>-0.06293023363851569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.662628817063316</v>
+        <v>2.764482930666063</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.594796824768422</v>
+        <v>-4.514203037407118</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9785936527440993</v>
+        <v>1.010831167688621</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2485763677760738</v>
+        <v>-0.07881951177149588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.667722986299572</v>
+        <v>2.769577099902318</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.771134584891351</v>
+        <v>-4.690540797530048</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9065945295195994</v>
+        <v>0.9388320444641207</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4249141278990032</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.560456311050486</v>
+        <v>2.662310424653232</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.770445212730128</v>
+        <v>-4.689851425368825</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9053618964240171</v>
+        <v>0.9375994113685386</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4249141278990032</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.558947929090414</v>
+        <v>2.660802042693161</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.777016177784721</v>
+        <v>-4.696422390423417</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9025963778376163</v>
+        <v>0.9348338927821378</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4314850929535961</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.554868217493095</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.769062207489949</v>
+        <v>-4.688468420128645</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9057779659555252</v>
+        <v>0.9380154809000465</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4314850929535961</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.554868217493095</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.758688831156862</v>
+        <v>-4.678095043795558</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9163090735165644</v>
+        <v>0.948546588461086</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4211117166205088</v>
+        <v>-0.2513548606159309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.567474000320752</v>
+        <v>2.669328113923498</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.631004521362565</v>
+        <v>-4.550410734001262</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9722751708090078</v>
+        <v>1.004512685753529</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2934274068262124</v>
+        <v>-0.1236705508216345</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.648976959572054</v>
+        <v>2.750831073174801</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.499618847980526</v>
+        <v>3.820465699482764</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.559069279500522</v>
+        <v>-4.61107732440365</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9878039400296974</v>
+        <v>0.967000722068446</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4129920161376368</v>
+        <v>-0.2053688675401681</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.563992866461072</v>
+        <v>2.688566755619553</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.820465699482764</v>
+        <v>3.820465699482766</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-45.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-657.3%</t>
+          <t>-657.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.7%</t>
+          <t>436.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-622.7%</t>
+          <t>-630.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.5%</t>
+          <t>-282.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-146.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-244.5%</t>
+          <t>-254.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.2%</t>
+          <t>-180.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1980"/>
+  <dimension ref="A1:G1981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.0129598482530679</v>
+        <v>0.01403231403089333</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.162338771597964</v>
+        <v>3.162767757909094</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.01799743898065442</v>
+        <v>0.01906990475847986</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.162931248074337</v>
+        <v>3.163360234385467</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1446286409839841</v>
+        <v>-0.1435561752061587</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.076627197712219</v>
+        <v>3.077056184023349</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2103960310333962</v>
+        <v>-0.2093235652555708</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.051337850822924</v>
+        <v>3.051766837134054</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4156407080906408</v>
+        <v>-0.4145682423128154</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.959868011987782</v>
+        <v>2.960296998298912</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4974126085183925</v>
+        <v>-0.496340142740567</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.917241977771919</v>
+        <v>2.91767096408305</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5646217163902701</v>
+        <v>-0.5635492506124447</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.895123651456871</v>
+        <v>2.895552637768001</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.772187500781882</v>
+        <v>-0.7711150350040565</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.809922133819466</v>
+        <v>2.810351120130596</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.189941524328719</v>
+        <v>-1.188869058550894</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.640747415905794</v>
+        <v>2.641176402216924</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.393230993650522</v>
+        <v>-1.392158527872696</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.559297844775995</v>
+        <v>2.559726831087125</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.601235052003599</v>
+        <v>-1.600162586225774</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.48098836598869</v>
+        <v>2.48141735229982</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.812647472891574</v>
+        <v>-1.811575007113749</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.391504853971488</v>
+        <v>2.391933840282618</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.151805850480097</v>
+        <v>-2.150733384702271</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.248925802242528</v>
+        <v>2.249354788553658</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.360296631931781</v>
+        <v>-2.359224166153955</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.185867779400622</v>
+        <v>2.186296765711753</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.607497816697003</v>
+        <v>-2.606425350919177</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.095086055903102</v>
+        <v>2.095515042214232</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.0998828447211</v>
+        <v>-3.098810378943274</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.899238436737196</v>
+        <v>1.899667423048326</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.485063235651172</v>
+        <v>-3.483990769873346</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.74370881917803</v>
+        <v>1.74413780548916</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.828746008877835</v>
+        <v>-3.827673543100009</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.608004833341981</v>
+        <v>1.608433819653111</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.035257785764856</v>
+        <v>-4.034185319987031</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.52150618124343</v>
+        <v>1.52193516755456</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.291098871543549</v>
+        <v>-4.290026405765723</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.420942673632212</v>
+        <v>1.421371659943343</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.722904664693337</v>
+        <v>-4.721832198915511</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.234553243839702</v>
+        <v>1.234982230150832</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.957598658825889</v>
+        <v>-4.956526193048063</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.128960421188772</v>
+        <v>1.129389407499902</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.293261306056341</v>
+        <v>-5.292188840278516</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9932759539525557</v>
+        <v>0.9937049402636862</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.656887550956655</v>
+        <v>-5.655815085178829</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8543130162266719</v>
+        <v>0.8547420025378023</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.022014933595401</v>
+        <v>-6.020942467817576</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7075165781770045</v>
+        <v>0.7079455644881349</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.430603710776079</v>
+        <v>-6.429531244998254</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5428426113194926</v>
+        <v>0.543271597630623</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.707179811091912</v>
+        <v>-6.706107345314086</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4273976036646201</v>
+        <v>0.4278265899757505</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.123571685378909</v>
+        <v>-7.122499219601083</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2588349045586984</v>
+        <v>0.2592638908698288</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.440183627919557</v>
+        <v>-7.439111162141732</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1424488182111183</v>
+        <v>0.1428778045222487</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.786058449904367</v>
+        <v>-7.784985984126541</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0001984545628896939</v>
+        <v>0.0006274408740201132</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.949638328088751</v>
+        <v>-7.948565862310925</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.06682857665586317</v>
+        <v>-0.06639959034473275</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.246299669898949</v>
+        <v>-8.245227204121123</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1817141374507343</v>
+        <v>-0.1812851511396039</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.451330850673266</v>
+        <v>-8.45025838489544</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2677529142948636</v>
+        <v>-0.2673239279837336</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.834332239415897</v>
+        <v>-8.833259773638071</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4210555711135004</v>
+        <v>-0.42062658480237</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.016202030400931</v>
+        <v>-9.015129564623106</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.491231971536084</v>
+        <v>-0.4908029852249536</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.375732352904933</v>
+        <v>-9.374659887127107</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6296937972396344</v>
+        <v>-0.6292648109285039</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.426081416359155</v>
+        <v>-9.425008950581329</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6419174026641459</v>
+        <v>-0.6414884163530155</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.523700693780551</v>
+        <v>-9.522628228002725</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6779233630109354</v>
+        <v>-0.6774943766998049</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.671226781786194</v>
+        <v>-9.670154316008368</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7340402418916203</v>
+        <v>-0.7336112555804899</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.875484957116058</v>
+        <v>-9.874412491338232</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8102303149049233</v>
+        <v>-0.8098013285937933</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.01729473132285</v>
+        <v>-10.01622226554502</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8624716701032029</v>
+        <v>-0.8620426837920721</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.943824899655397</v>
+        <v>-9.942752433877571</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8177120359428018</v>
+        <v>-0.8172830496316714</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.11894931704194</v>
+        <v>-10.11787685126411</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8732065821499022</v>
+        <v>-0.8727775958387722</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.35340141105643</v>
+        <v>-10.3523289452786</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9742065846572943</v>
+        <v>-0.9737775983461643</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.64120525559367</v>
+        <v>-10.64013278981584</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.096000313246166</v>
+        <v>-1.095571326935036</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390588</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.69399141119399</v>
+        <v>-10.69291894541617</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.115998985647741</v>
+        <v>-1.11556999933661</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297402</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.92602033093026</v>
+        <v>-10.92494786515243</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.20611682491313</v>
+        <v>-1.205687838602</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.87400481696144</v>
+        <v>-10.87293235118362</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.181320283639204</v>
+        <v>-1.180891297328074</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.01567665868556</v>
+        <v>-11.01460419290774</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.239464247227594</v>
+        <v>-1.239035260916464</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.96608581426073</v>
+        <v>-10.9650133484829</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.204574499292788</v>
+        <v>-1.204145512981658</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.76693370702363</v>
+        <v>-10.7658612412458</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.137964790044631</v>
+        <v>-1.137535803733501</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.54108855430422</v>
+        <v>-10.54001608852639</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.038047655920658</v>
+        <v>-1.037618669609528</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.41650989796663</v>
+        <v>-10.4154374321888</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9870770488295633</v>
+        <v>-0.9866480625184324</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.46940518601092</v>
+        <v>-10.46833272023309</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.00560138988517</v>
+        <v>-1.005172403574039</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.18549645508217</v>
+        <v>-10.18442398930434</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8863041932750342</v>
+        <v>-0.8858752069639033</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.11413006247252</v>
+        <v>-10.11305759669469</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8674948986250399</v>
+        <v>-0.8670659123139091</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.850293195268449</v>
+        <v>-9.849220729490622</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7718436330563199</v>
+        <v>-0.771414646745189</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.583051394400051</v>
+        <v>-9.581978928622224</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6667814732083346</v>
+        <v>-0.6663524868972037</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.485144355723561</v>
+        <v>-9.484071889945733</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6279189727111993</v>
+        <v>-0.627489986400068</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.461190814747603</v>
+        <v>-9.460118348969775</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6176690501753224</v>
+        <v>-0.6172400638641915</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.197130876424806</v>
+        <v>-9.196058410646978</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5253053910079557</v>
+        <v>-0.5248764046968248</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.490051252919969</v>
+        <v>-8.488978787142141</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2452605752663217</v>
+        <v>-0.2448315889551909</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.449866954553778</v>
+        <v>-8.448794488775951</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2288432320320042</v>
+        <v>-0.2284142457208733</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.369797159015974</v>
+        <v>-8.368724693238146</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1974484925961253</v>
+        <v>-0.1970195062849944</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.136315936786374</v>
+        <v>-8.135243471008547</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09613157486643331</v>
+        <v>-0.09570258855530245</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.986649545778859</v>
+        <v>-7.985577080001032</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03915722877638661</v>
+        <v>-0.0387282424652553</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.854374072147973</v>
+        <v>-7.853301606370145</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.009120447422995337</v>
+        <v>0.0095494337341262</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.66377439747482</v>
+        <v>-7.746329832319156</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.08817537797989283</v>
+        <v>0.05515320404215851</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.522487602763774</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.240548999625305</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.414774598791239</v>
+        <v>-7.497330033635575</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2006816386769841</v>
+        <v>0.1676594647392498</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.522487602763774</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.253455340848963</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.520364588564344</v>
+        <v>-7.60292002340868</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03046971316852343</v>
+        <v>-0.002552460769210896</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.628077592536878</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.062125417385882</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.539099490682941</v>
+        <v>-7.621654925527277</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07152009419817107</v>
+        <v>0.03849792026043675</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.628077592536878</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.110669759262968</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.391159449275341</v>
+        <v>-7.473714884119677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01081718807304322</v>
+        <v>-0.02220498586469111</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.60775667662832</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>2.002983386119936</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.374001299144047</v>
+        <v>-7.456556733988383</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.008966461872082832</v>
+        <v>-0.02405571206565149</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.590598526497026</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>2.004564289945233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.330452892373357</v>
+        <v>-7.413008327217693</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01942521248526585</v>
+        <v>-0.01359696145246847</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.590598526497026</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>1.99760367785014</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.088304498919499</v>
+        <v>-7.170859933763834</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1307469242479522</v>
+        <v>0.09772475031021788</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.590598526497026</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>2.012066032231283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.980045361796977</v>
+        <v>-7.062600796641313</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1685826995561559</v>
+        <v>0.1355605256184216</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.590598526497026</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>2.006598152690478</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.856754226979846</v>
+        <v>-6.939309661824182</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.215397247493585</v>
+        <v>0.1823750735558507</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.467307391679896</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.078070927591334</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.835605028076403</v>
+        <v>-6.918160462920738</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2315579052922878</v>
+        <v>0.1985357313545535</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.446158192776452</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.098461425170725</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.591839586092958</v>
+        <v>-6.674395020937294</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3248447904327159</v>
+        <v>0.2918226164949815</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.446158192776452</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.094242133517776</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.444942558375088</v>
+        <v>-6.527497993219423</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3857279154398805</v>
+        <v>0.3527057415021462</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.398499950797864</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.124961392624944</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.195092164426013</v>
+        <v>-6.277647599270349</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4784101480032121</v>
+        <v>0.4453879740654778</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.398499950797864</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.117703467608647</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.019200071958581</v>
+        <v>-6.101755506802917</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5523661085108338</v>
+        <v>0.5193439345730995</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.398499950797864</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.121302591129295</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.847753608936118</v>
+        <v>-5.930309043780453</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6342721997743732</v>
+        <v>0.6012500258366389</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.227053487775401</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.237497974997327</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.622720609267295</v>
+        <v>-5.70527604411163</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7233058772581993</v>
+        <v>0.690283703320465</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-1.002020488106578</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.371538252414918</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.55908486703336</v>
+        <v>-5.641640301877696</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7534549752060902</v>
+        <v>0.7204328012683558</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.9383847458726436</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.414414498809596</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.466084825827462</v>
+        <v>-5.548640260671798</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7718492504722452</v>
+        <v>0.7388270765345109</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.9383847458726436</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.395608757593391</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.225654329022602</v>
+        <v>-5.308209763866937</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8697645258190665</v>
+        <v>0.8367423518813322</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6979542490677834</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.541610132301185</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.153411760851407</v>
+        <v>-5.235967195695743</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9025908669223646</v>
+        <v>0.8695686929846302</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6979542490677834</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.545539446136005</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.100413438570019</v>
+        <v>-5.182968873414355</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9244687797522597</v>
+        <v>0.8914466058145254</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.6426179900658445</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.579419785454508</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.991608553090292</v>
+        <v>-5.074163987934628</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9649888051641442</v>
+        <v>0.9319666312264099</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.6426179900658445</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.576417856674502</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.771587755053281</v>
+        <v>-4.854143189897617</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.054576161389563</v>
+        <v>1.021553987451828</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5013981449978643</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.662728800725904</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.638720065990004</v>
+        <v>-4.72127550083434</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.123617419816697</v>
+        <v>1.090595245878963</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5013981449978643</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.678622983527728</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.479204962470634</v>
+        <v>-4.56176039731497</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.188569305664747</v>
+        <v>1.155547131727012</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.3418830414784944</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.775477890079651</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.334532817370897</v>
+        <v>-4.417088252215232</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.256526266266082</v>
+        <v>1.223504092328347</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.1972108963787569</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.872369279700933</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.394407644728589</v>
+        <v>-4.476963079572925</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.21861382672443</v>
+        <v>1.185591652786696</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.2570857237364491</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.822481874687744</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.30760814694958</v>
+        <v>-4.390163581793916</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.2757341191586</v>
+        <v>1.242711945220866</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.2570857237364491</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.84488236801031</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.310077853411386</v>
+        <v>-4.392633288255722</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.27481863794729</v>
+        <v>1.241796464009556</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.2595554301982552</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.843472945506639</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.378448039735396</v>
+        <v>-4.461003474579732</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.258477485892388</v>
+        <v>1.225455311954654</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2502797311620403</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.86004528740307</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.48698622065153</v>
+        <v>-4.569541655495866</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.205498922157826</v>
+        <v>1.172476748220091</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2502797311620403</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.850481996034961</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.517979379980235</v>
+        <v>-4.600534814824571</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.01781122346673</v>
+        <v>0.9847890495289959</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2502797311620403</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.675191561075348</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.342505120187766</v>
+        <v>-4.425060555032102</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.092568159375506</v>
+        <v>1.059545985437771</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2502797311620403</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.679758793067136</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.453441372829015</v>
+        <v>-4.535996807673351</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.023935687080213</v>
+        <v>0.9909135131424787</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2502797311620403</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.655500821828343</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.656467950372249</v>
+        <v>-4.739023385216584</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9458564412828254</v>
+        <v>0.9128342673450911</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.4533063087052737</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.536816260522308</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.498542351436956</v>
+        <v>-4.581097786281291</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019199067289075</v>
+        <v>0.9861768933513406</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.4533063087052737</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.54698864695444</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.412298888410578</v>
+        <v>-4.494854323254914</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.048642723073486</v>
+        <v>1.015620549135752</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.4533063087052737</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.541934917528301</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.457605707809558</v>
+        <v>-4.540161142653893</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.02229577075842</v>
+        <v>0.9892735968206856</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.4941164717145045</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.569256935152479</v>
+        <v>2.509224595167288</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.486638812511859</v>
+        <v>-4.569194247356195</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.011234401910601</v>
+        <v>0.9782122279728667</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.4941164717145045</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569808808185581</v>
+        <v>2.509776468200389</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.393828331060999</v>
+        <v>-4.476383765905335</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9776312863823104</v>
+        <v>0.9446091124445761</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3012520902883266</v>
+        <v>-0.4013059902636451</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554767788947462</v>
+        <v>2.49473544896227</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.345265278839969</v>
+        <v>-4.427820713684305</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9989299831953233</v>
+        <v>0.965907809257589</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2526890380672964</v>
+        <v>-0.3527429380426149</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.585779096204681</v>
+        <v>2.52574675621949</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.232594060603719</v>
+        <v>-4.315149495448055</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.039074179001546</v>
+        <v>1.006052005063812</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.2400717198063647</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.648457535658154</v>
+        <v>2.588425195672963</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.120217059421046</v>
+        <v>-4.202772494265382</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.089516275305283</v>
+        <v>1.056494101367548</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.2400717198063647</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.653948831488821</v>
+        <v>2.59391649150363</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.318451628307777</v>
+        <v>-4.401007063152113</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.02171964951913</v>
+        <v>0.9886974755813953</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3382523887177767</v>
+        <v>-0.4383062886930953</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.546505291925322</v>
+        <v>2.486472951940131</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.401452909333056</v>
+        <v>-4.484008344177392</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8268748571096713</v>
+        <v>0.793852683171937</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4568771732202691</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.373718481209671</v>
+        <v>2.31368614122448</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.528519915640044</v>
+        <v>-4.61107535048438</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8961977153060816</v>
+        <v>0.8631755413683473</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4568771732202691</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.493868141928877</v>
+        <v>2.433835801943685</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.615118498621147</v>
+        <v>-4.697673933465483</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8760713082159635</v>
+        <v>0.8430491342782291</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4568771732202691</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.5083811680312</v>
+        <v>2.448348828046008</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.576734836062996</v>
+        <v>-4.659290270907332</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8888442145815927</v>
+        <v>0.8558220406438584</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.4184935106621179</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.528830806908459</v>
+        <v>2.468798466923268</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.39961850602783</v>
+        <v>-4.482173940872165</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9564197754409609</v>
+        <v>0.9233976015032266</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.4184935106621179</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.525559835753761</v>
+        <v>2.46552749576857</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.369916382051536</v>
+        <v>-4.452471816895872</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9689840167933914</v>
+        <v>0.9359618428556571</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3229097359021127</v>
+        <v>-0.4229636358774312</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.523561152386486</v>
+        <v>2.463528812401295</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.190540960812768</v>
+        <v>-4.273096395657104</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.034521160595313</v>
+        <v>1.001498986657579</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.166132977731394</v>
+        <v>-0.2661868777067126</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.611414182595332</v>
+        <v>2.55138184261014</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.235555174333374</v>
+        <v>-4.31811060917771</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9973229305186604</v>
+        <v>0.9643007565809261</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1964818730459986</v>
+        <v>-0.2965357730213172</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.574012300738159</v>
+        <v>2.513979960752967</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.502559684605809</v>
+        <v>-4.585115119450145</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8962126887486321</v>
+        <v>0.8631905148108978</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3908449110889472</v>
+        <v>-0.4908988110642657</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.463086040251335</v>
+        <v>2.403053700266144</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.603757466042982</v>
+        <v>-4.686312900887318</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8549374980702644</v>
+        <v>0.8219153241325301</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5593076246095849</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.421244674020645</v>
+        <v>2.361212334035454</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.57128187987221</v>
+        <v>-4.653837314716545</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.86552769409289</v>
+        <v>0.8325055201551557</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5593076246095849</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.418844635574962</v>
+        <v>2.35881229558977</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.552243752164912</v>
+        <v>-4.634799187009248</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.869667664384054</v>
+        <v>0.8366454904463196</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6174912359407795</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.320426847999299</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.583370383315531</v>
+        <v>-4.665925818159867</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.034798880862487</v>
+        <v>1.001776706924753</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6174912359407795</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.498008716937979</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.635690763916323</v>
+        <v>-4.718246198760658</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.014704057608304</v>
+        <v>0.9816818836705696</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.5825443759319073</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.519810161929436</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.780013669841241</v>
+        <v>-4.862569104685577</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9629834256352623</v>
+        <v>0.929961251697528</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.5825443759319073</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.525818692326362</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.632270699606239</v>
+        <v>-4.714826134450575</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.101233261521285</v>
+        <v>1.068211087583551</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4147370186970242</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.705655754459314</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.73428538213746</v>
+        <v>-4.816840816981796</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.063221010040278</v>
+        <v>1.030198836102543</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4147370186970242</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.708449375990795</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.597676038043367</v>
+        <v>-4.680231472887703</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.118527096069573</v>
+        <v>1.085504922131839</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.2781276746029317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.791077330838909</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.740441370866018</v>
+        <v>-4.822996805710353</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.060501439680623</v>
+        <v>1.027479265742889</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4208930074255821</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.704498607885429</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.678143372089895</v>
+        <v>-4.760698806934231</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.151756192987893</v>
+        <v>1.118734019050159</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4208930074255821</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.77083416168225</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.476353174424737</v>
+        <v>-4.558908609269073</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9410531444433543</v>
+        <v>0.90803097050562</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.2228748152564277</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.59822594937314</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.416462492782144</v>
+        <v>-4.49901792762648</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.035299649422567</v>
+        <v>1.002277475484833</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.1629841336138342</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.704450590680871</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.514203037407118</v>
+        <v>-4.596758472251454</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.010831167688621</v>
+        <v>0.9778089937508865</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.1788734117468144</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.709544759917127</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.690540797530048</v>
+        <v>-4.773096232374384</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9388320444641207</v>
+        <v>0.9058098705263864</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.3552111718697438</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.602278084668041</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.689851425368825</v>
+        <v>-4.77240686021316</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9375994113685386</v>
+        <v>0.9045772374308043</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.3552111718697438</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.60076970270797</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.696422390423417</v>
+        <v>-4.778977825267753</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9348338927821378</v>
+        <v>0.9018117188444035</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.3617821369243368</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.59668999111065</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.688468420128645</v>
+        <v>-4.771023854972981</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9380154809000465</v>
+        <v>0.9049933069623122</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.3617821369243368</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.59668999111065</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.678095043795558</v>
+        <v>-4.760650478639894</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.948546588461086</v>
+        <v>0.9155244145233516</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.3514087605912495</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.609295773938307</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.550410734001262</v>
+        <v>-4.632966168845598</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.004512685753529</v>
+        <v>0.971490511815795</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1236705508216345</v>
+        <v>-0.223724450796953</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.750831073174801</v>
+        <v>2.690798733189609</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,45 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.820465699482766</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.61107732440365</v>
+        <v>-4.693632759247986</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.967000722068446</v>
+        <v>0.9339785481307117</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2053688675401681</v>
+        <v>-0.3054227675154867</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.688566755619553</v>
+        <v>2.628534415634362</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B1981" t="n">
+        <v>3.509562338442501</v>
+      </c>
+      <c r="C1981" t="n">
+        <v>2.658724842907396</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>-4.693632759247986</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>0.9339785481307117</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>-0.3054227675154867</v>
+      </c>
+      <c r="G1981" t="n">
+        <v>2.651788639893764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-657.2%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>436.6%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.9%</t>
+          <t>-640.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-263.3%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.8%</t>
+          <t>-286.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.8%</t>
+          <t>-146.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.5%</t>
+          <t>-254.0%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.01403231403089333</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.162767757909094</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.01906990475847986</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.163360234385467</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1435561752061587</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.077056184023349</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2093235652555708</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.051766837134054</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4145682423128154</v>
+        <v>-0.4962344954519427</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.960296998298912</v>
+        <v>2.927630497043261</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.496340142740567</v>
+        <v>-0.5780063958796944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.91767096408305</v>
+        <v>2.885004462827399</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5635492506124447</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.895552637768001</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7711150350040565</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.810351120130596</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.188869058550894</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.641176402216924</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.392158527872696</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.559726831087125</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.600162586225774</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.48141735229982</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.811575007113749</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.391933840282618</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.150733384702271</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.249354788553658</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.359224166153955</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.186296765711753</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.606425350919177</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.095515042214232</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.098810378943274</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.899667423048326</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.483990769873346</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.74413780548916</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.827673543100009</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.608433819653111</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.034185319987031</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.52193516755456</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.290026405765723</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.421371659943343</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.721832198915511</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.234982230150832</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.956526193048063</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.129389407499902</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.292188840278516</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9937049402636862</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.655815085178829</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8547420025378023</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.020942467817576</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7079455644881349</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.429531244998254</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.543271597630623</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.706107345314086</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4278265899757505</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.122499219601083</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2592638908698288</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.439111162141732</v>
+        <v>-7.520777415280859</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1428778045222487</v>
+        <v>0.1102113032665977</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.784985984126541</v>
+        <v>-7.866652237265669</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0006274408740201132</v>
+        <v>-0.03203906038163096</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.948565862310925</v>
+        <v>-8.030232115450053</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.06639959034473275</v>
+        <v>-0.09906609160038382</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.245227204121123</v>
+        <v>-8.326893457260251</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1812851511396039</v>
+        <v>-0.2139516523952549</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.45025838489544</v>
+        <v>-8.531924638034567</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2673239279837336</v>
+        <v>-0.2999904292393847</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.833259773638071</v>
+        <v>-8.914926026777199</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.42062658480237</v>
+        <v>-0.4532930860580211</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.015129564623106</v>
+        <v>-9.096795817762233</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4908029852249536</v>
+        <v>-0.5234694864806047</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.374659887127107</v>
+        <v>-9.456326140266235</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6292648109285039</v>
+        <v>-0.661931312184155</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.425008950581329</v>
+        <v>-9.506675203720457</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6414884163530155</v>
+        <v>-0.6741549176086665</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.522628228002725</v>
+        <v>-9.604294481141853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6774943766998049</v>
+        <v>-0.710160877955456</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.670154316008368</v>
+        <v>-9.751820569147496</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7336112555804899</v>
+        <v>-0.766277756836141</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.874412491338232</v>
+        <v>-9.95607874447736</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8098013285937933</v>
+        <v>-0.8424678298494443</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.01622226554502</v>
+        <v>-10.09788851868415</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8620426837920721</v>
+        <v>-0.8947091850477231</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.942752433877571</v>
+        <v>-10.0244186870167</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8172830496316714</v>
+        <v>-0.8499495508873229</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.11787685126411</v>
+        <v>-10.19954310440324</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8727775958387722</v>
+        <v>-0.9054440970944233</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.3523289452786</v>
+        <v>-10.43399519841773</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9737775983461643</v>
+        <v>-1.006444099601815</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.64013278981584</v>
+        <v>-10.72179904295497</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.095571326935036</v>
+        <v>-1.128237828190687</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.69291894541617</v>
+        <v>-10.7745851985553</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.11556999933661</v>
+        <v>-1.148236500592261</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.92494786515243</v>
+        <v>-11.00661411829156</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.205687838602</v>
+        <v>-1.238354339857651</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.87293235118362</v>
+        <v>-10.95459860432275</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.180891297328074</v>
+        <v>-1.213557798583725</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.01460419290774</v>
+        <v>-11.09627044604687</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.239035260916464</v>
+        <v>-1.271701762172115</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.9650133484829</v>
+        <v>-11.04667960162203</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.204145512981658</v>
+        <v>-1.236812014237309</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.7658612412458</v>
+        <v>-10.84752749438493</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.137535803733501</v>
+        <v>-1.170202304989152</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.54001608852639</v>
+        <v>-10.62168234166552</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.037618669609528</v>
+        <v>-1.070285170865179</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.4154374321888</v>
+        <v>-10.49710368532793</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9866480625184324</v>
+        <v>-1.019314563774083</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.46833272023309</v>
+        <v>-10.54999897337222</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.005172403574039</v>
+        <v>-1.037838904829691</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.18442398930434</v>
+        <v>-10.26609024244347</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8858752069639033</v>
+        <v>-0.9185417082195544</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.11305759669469</v>
+        <v>-10.19472384983382</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8670659123139091</v>
+        <v>-0.899732413569561</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.849220729490622</v>
+        <v>-9.930886982629751</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.771414646745189</v>
+        <v>-0.8040811480008405</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.581978928622224</v>
+        <v>-9.663645181761353</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6663524868972037</v>
+        <v>-0.6990189881528552</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.484071889945733</v>
+        <v>-9.565738143084863</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.627489986400068</v>
+        <v>-0.66015648765572</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.460118348969775</v>
+        <v>-9.541784602108905</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6172400638641915</v>
+        <v>-0.649906565119843</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.196058410646978</v>
+        <v>-9.277724663786108</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5248764046968248</v>
+        <v>-0.5575429059524764</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.488978787142141</v>
+        <v>-8.570645040281271</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2448315889551909</v>
+        <v>-0.2774980902108424</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.448794488775951</v>
+        <v>-8.53046074191508</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2284142457208733</v>
+        <v>-0.2610807469765248</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.368724693238146</v>
+        <v>-8.450390946377276</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1970195062849944</v>
+        <v>-0.2296860075406464</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.135243471008547</v>
+        <v>-8.216909724147676</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09570258855530245</v>
+        <v>-0.128369089810954</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.985577080001032</v>
+        <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0387282424652553</v>
+        <v>-0.07139474372090771</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.853301606370145</v>
+        <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.0095494337341262</v>
+        <v>-0.02311706752152576</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.746329832319156</v>
+        <v>-7.838729032049837</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05515320404215851</v>
+        <v>0.01819352414988629</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.522487602763774</v>
+        <v>-1.51679455000217</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.240548999625305</v>
+        <v>2.243964831282267</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.497330033635575</v>
+        <v>-7.589729233366256</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1676594647392498</v>
+        <v>0.1306997848469771</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.522487602763774</v>
+        <v>-1.51679455000217</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.253455340848963</v>
+        <v>2.256871172505925</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.60292002340868</v>
+        <v>-7.695319223139361</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.002552460769210896</v>
+        <v>-0.03951214066148312</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.628077592536878</v>
+        <v>-1.622384539775274</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.062125417385882</v>
+        <v>2.065541249042844</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.621654925527277</v>
+        <v>-7.714054125257958</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03849792026043675</v>
+        <v>0.001538240368164523</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.628077592536878</v>
+        <v>-1.622384539775274</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.110669759262968</v>
+        <v>2.114085590919931</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.473714884119677</v>
+        <v>-7.566114083850358</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02220498586469111</v>
+        <v>-0.05916466575696333</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.60775667662832</v>
+        <v>-1.602063623866717</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.002983386119936</v>
+        <v>2.006399217776898</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.456556733988383</v>
+        <v>-7.548955933719064</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02405571206565149</v>
+        <v>-0.06101539195792416</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.590598526497026</v>
+        <v>-1.584905473735422</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.004564289945233</v>
+        <v>2.007980121602196</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.413008327217693</v>
+        <v>-7.505407526948374</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01359696145246847</v>
+        <v>-0.05055664134474114</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.590598526497026</v>
+        <v>-1.584905473735422</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.99760367785014</v>
+        <v>2.001019509507103</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.170859933763834</v>
+        <v>-7.263259133494516</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09772475031021788</v>
+        <v>0.06076507041794521</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.590598526497026</v>
+        <v>-1.584905473735422</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.012066032231283</v>
+        <v>2.015481863888246</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.062600796641313</v>
+        <v>-7.154999996371994</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1355605256184216</v>
+        <v>0.09860084572614891</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.590598526497026</v>
+        <v>-1.584905473735422</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.006598152690478</v>
+        <v>2.010013984347441</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.939309661824182</v>
+        <v>-7.031708861554863</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1823750735558507</v>
+        <v>0.1454153936635785</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.467307391679896</v>
+        <v>-1.461614338918292</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.078070927591334</v>
+        <v>2.081486759248296</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.918160462920738</v>
+        <v>-7.01055966265142</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1985357313545535</v>
+        <v>0.1615760514622808</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.446158192776452</v>
+        <v>-1.440465140014848</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.098461425170725</v>
+        <v>2.101877256827688</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.674395020937294</v>
+        <v>-6.766794220667975</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2918226164949815</v>
+        <v>0.2548629366027093</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.446158192776452</v>
+        <v>-1.440465140014848</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.094242133517776</v>
+        <v>2.097657965174738</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.527497993219423</v>
+        <v>-6.619897192950106</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3527057415021462</v>
+        <v>0.3157460616098731</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.398499950797864</v>
+        <v>-1.39280689803626</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.124961392624944</v>
+        <v>2.128377224281907</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.277647599270349</v>
+        <v>-6.370046799001031</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4453879740654778</v>
+        <v>0.4084282941732051</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.398499950797864</v>
+        <v>-1.39280689803626</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.117703467608647</v>
+        <v>2.121119299265609</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.101755506802917</v>
+        <v>-6.194154706533599</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5193439345730995</v>
+        <v>0.4823842546808268</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.398499950797864</v>
+        <v>-1.39280689803626</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.121302591129295</v>
+        <v>2.124718422786258</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.930309043780453</v>
+        <v>-6.022708243511135</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6012500258366389</v>
+        <v>0.5642903459443658</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.227053487775401</v>
+        <v>-1.221360435013797</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.237497974997327</v>
+        <v>2.240913806654289</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.70527604411163</v>
+        <v>-5.797675243842312</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.690283703320465</v>
+        <v>0.6533240234281918</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.002020488106578</v>
+        <v>-0.9963274353449744</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.371538252414918</v>
+        <v>2.37495408407188</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.641640301877696</v>
+        <v>-5.734039501608378</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7204328012683558</v>
+        <v>0.6834731213760832</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9383847458726436</v>
+        <v>-0.9326916931110398</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.414414498809596</v>
+        <v>2.417830330466558</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.548640260671798</v>
+        <v>-5.64103946040248</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7388270765345109</v>
+        <v>0.7018673966422382</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9383847458726436</v>
+        <v>-0.9326916931110398</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.395608757593391</v>
+        <v>2.399024589250354</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.308209763866937</v>
+        <v>-5.40060896359762</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8367423518813322</v>
+        <v>0.7997826719890595</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6979542490677834</v>
+        <v>-0.6922611963061795</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.541610132301185</v>
+        <v>2.545025963958147</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.235967195695743</v>
+        <v>-5.328366395426425</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8695686929846302</v>
+        <v>0.8326090130923576</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6979542490677834</v>
+        <v>-0.6922611963061795</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.545539446136005</v>
+        <v>2.548955277792967</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.182968873414355</v>
+        <v>-5.275368073145037</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8914466058145254</v>
+        <v>0.8544869259222527</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6426179900658445</v>
+        <v>-0.6369249373042407</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.579419785454508</v>
+        <v>2.582835617111471</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.074163987934628</v>
+        <v>-5.16656318766531</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9319666312264099</v>
+        <v>0.8950069513341372</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6426179900658445</v>
+        <v>-0.6369249373042407</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.576417856674502</v>
+        <v>2.579833688331464</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.854143189897617</v>
+        <v>-4.946542389628299</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.021553987451828</v>
+        <v>0.9845943075595553</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5013981449978643</v>
+        <v>-0.4957050922362605</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.662728800725904</v>
+        <v>2.666144632382867</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.72127550083434</v>
+        <v>-4.813674700565022</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.090595245878963</v>
+        <v>1.05363556598669</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5013981449978643</v>
+        <v>-0.4957050922362605</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.678622983527728</v>
+        <v>2.68203881518469</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.56176039731497</v>
+        <v>-4.654159597045652</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.155547131727012</v>
+        <v>1.11858745183474</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3418830414784944</v>
+        <v>-0.3361899887168905</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.775477890079651</v>
+        <v>2.778893721736614</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.417088252215232</v>
+        <v>-4.509487451945914</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.223504092328347</v>
+        <v>1.186544412436074</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1972108963787569</v>
+        <v>-0.1915178436171531</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.872369279700933</v>
+        <v>2.875785111357896</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.476963079572925</v>
+        <v>-4.569362279303607</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.185591652786696</v>
+        <v>1.148631972894423</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2570857237364491</v>
+        <v>-0.2513926709748452</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.822481874687744</v>
+        <v>2.825897706344707</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.390163581793916</v>
+        <v>-4.482562781524598</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.242711945220866</v>
+        <v>1.205752265328593</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2570857237364491</v>
+        <v>-0.2513926709748452</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.84488236801031</v>
+        <v>2.848298199667273</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.392633288255722</v>
+        <v>-4.485032487986404</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.241796464009556</v>
+        <v>1.204836784117283</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2595554301982552</v>
+        <v>-0.2538623774366514</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.843472945506639</v>
+        <v>2.846888777163601</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.461003474579732</v>
+        <v>-4.553402674310414</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.225455311954654</v>
+        <v>1.188495632062381</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2502797311620403</v>
+        <v>-0.2445866784004365</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.86004528740307</v>
+        <v>2.863461119060032</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.569541655495866</v>
+        <v>-4.661940855226548</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.172476748220091</v>
+        <v>1.135517068327818</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2502797311620403</v>
+        <v>-0.2445866784004365</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.850481996034961</v>
+        <v>2.853897827691923</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.600534814824571</v>
+        <v>-4.692934014555253</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9847890495289959</v>
+        <v>0.947829369636723</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2502797311620403</v>
+        <v>-0.2445866784004365</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.675191561075348</v>
+        <v>2.67860739273231</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.425060555032102</v>
+        <v>-4.517459754762784</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.059545985437771</v>
+        <v>1.022586305545498</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2502797311620403</v>
+        <v>-0.2445866784004365</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.679758793067136</v>
+        <v>2.683174624724098</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.535996807673351</v>
+        <v>-4.628396007404033</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9909135131424787</v>
+        <v>0.953953833250206</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2502797311620403</v>
+        <v>-0.2445866784004365</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.655500821828343</v>
+        <v>2.658916653485305</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.739023385216584</v>
+        <v>-4.831422584947267</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9128342673450911</v>
+        <v>0.8758745874528182</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4533063087052737</v>
+        <v>-0.4476132559436699</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.536816260522308</v>
+        <v>2.54023209217927</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.78434395226416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.581097786281291</v>
+        <v>-4.673496986011973</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9861768933513406</v>
+        <v>0.9492172134590677</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4533063087052737</v>
+        <v>-0.4476132559436699</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.54698864695444</v>
+        <v>2.550404478611403</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.494854323254914</v>
+        <v>-4.587253522985596</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.015620549135752</v>
+        <v>0.9786608692434791</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4533063087052737</v>
+        <v>-0.4476132559436699</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.541934917528301</v>
+        <v>2.545350749185263</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.540161142653893</v>
+        <v>-4.632560342384576</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9892735968206856</v>
+        <v>0.9523139169284127</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4941164717145045</v>
+        <v>-0.4884234189529006</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.509224595167288</v>
+        <v>2.51264042682425</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.569194247356195</v>
+        <v>-4.661593447086877</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9782122279728667</v>
+        <v>0.9412525480805938</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4941164717145045</v>
+        <v>-0.4884234189529006</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.509776468200389</v>
+        <v>2.513192299857351</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.476383765905335</v>
+        <v>-4.568782965636017</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9446091124445761</v>
+        <v>0.9076494325523035</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4013059902636451</v>
+        <v>-0.3956129375020413</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.49473544896227</v>
+        <v>2.498151280619233</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.427820713684305</v>
+        <v>-4.520219913414987</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.965907809257589</v>
+        <v>0.9289481293653161</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3527429380426149</v>
+        <v>-0.3470498852810111</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.52574675621949</v>
+        <v>2.529162587876452</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.315149495448055</v>
+        <v>-4.407548695178737</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.006052005063812</v>
+        <v>0.9690923251715393</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2400717198063647</v>
+        <v>-0.2343786670447609</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.588425195672963</v>
+        <v>2.591841027329925</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.202772494265382</v>
+        <v>-4.295171693996064</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.056494101367548</v>
+        <v>1.019534421475276</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2400717198063647</v>
+        <v>-0.2343786670447609</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.59391649150363</v>
+        <v>2.597332323160592</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.401007063152113</v>
+        <v>-4.493406262882795</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9886974755813953</v>
+        <v>0.9517377956891224</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4383062886930953</v>
+        <v>-0.4326132359314915</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.486472951940131</v>
+        <v>2.489888783597093</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.484008344177392</v>
+        <v>-4.576407543908074</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.793852683171937</v>
+        <v>0.7568930032796641</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4568771732202691</v>
+        <v>-0.4511841204586652</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.31368614122448</v>
+        <v>2.317101972881442</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.61107535048438</v>
+        <v>-4.703474550215062</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8631755413683473</v>
+        <v>0.8262158614760744</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4568771732202691</v>
+        <v>-0.4511841204586652</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.433835801943685</v>
+        <v>2.437251633600648</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.697673933465483</v>
+        <v>-4.790073133196165</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8430491342782291</v>
+        <v>0.8060894543859562</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4568771732202691</v>
+        <v>-0.4511841204586652</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.448348828046008</v>
+        <v>2.451764659702971</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.659290270907332</v>
+        <v>-4.751689470638014</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8558220406438584</v>
+        <v>0.8188623607515855</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4184935106621179</v>
+        <v>-0.4128004579005141</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.468798466923268</v>
+        <v>2.47221429858023</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.482173940872165</v>
+        <v>-4.574573140602848</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9233976015032266</v>
+        <v>0.8864379216109537</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4184935106621179</v>
+        <v>-0.4128004579005141</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.46552749576857</v>
+        <v>2.468943327425532</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.452471816895872</v>
+        <v>-4.544871016626554</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9359618428556571</v>
+        <v>0.8990021629633844</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4229636358774312</v>
+        <v>-0.4172705831158274</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.463528812401295</v>
+        <v>2.466944644058257</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273096395657104</v>
+        <v>-4.365495595387786</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001498986657579</v>
+        <v>0.9645393067653059</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2661868777067126</v>
+        <v>-0.2604938249451088</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.55138184261014</v>
+        <v>2.554797674267102</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.31811060917771</v>
+        <v>-4.410509808908392</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9643007565809261</v>
+        <v>0.9273410766886532</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2965357730213172</v>
+        <v>-0.2908427202597134</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.513979960752967</v>
+        <v>2.51739579240993</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585115119450145</v>
+        <v>-4.677514319180827</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8631905148108978</v>
+        <v>0.8262308349186249</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4908988110642657</v>
+        <v>-0.4852057583026619</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.403053700266144</v>
+        <v>2.406469531923106</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686312900887318</v>
+        <v>-4.778712100618</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8219153241325301</v>
+        <v>0.7849556442402572</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5593076246095849</v>
+        <v>-0.5536145718479811</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.361212334035454</v>
+        <v>2.364628165692416</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.653837314716545</v>
+        <v>-4.746236514447228</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8325055201551557</v>
+        <v>0.795545840262883</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5593076246095849</v>
+        <v>-0.5536145718479811</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.35881229558977</v>
+        <v>2.362228127246733</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.634799187009248</v>
+        <v>-4.72719838673993</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8366454904463196</v>
+        <v>0.7996858105540467</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6174912359407795</v>
+        <v>-0.6117981831791757</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.320426847999299</v>
+        <v>2.323842679656261</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.665925818159867</v>
+        <v>-4.758325017890549</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001776706924753</v>
+        <v>0.9648170270324798</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6174912359407795</v>
+        <v>-0.6117981831791757</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.498008716937979</v>
+        <v>2.501424548594942</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.718246198760658</v>
+        <v>-4.81064539849134</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9816818836705696</v>
+        <v>0.9447222037782967</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5825443759319073</v>
+        <v>-0.5768513231703035</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.519810161929436</v>
+        <v>2.523225993586399</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.862569104685577</v>
+        <v>-4.954968304416259</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.929961251697528</v>
+        <v>0.8930015718052551</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5825443759319073</v>
+        <v>-0.5768513231703035</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.525818692326362</v>
+        <v>2.529234523983324</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.714826134450575</v>
+        <v>-4.807225334181257</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.068211087583551</v>
+        <v>1.031251407691278</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4147370186970242</v>
+        <v>-0.4090439659354204</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.705655754459314</v>
+        <v>2.709071586116276</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.816840816981796</v>
+        <v>-4.909240016712478</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.030198836102543</v>
+        <v>0.9932391562102705</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4147370186970242</v>
+        <v>-0.4090439659354204</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.708449375990795</v>
+        <v>2.711865207647757</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.680231472887703</v>
+        <v>-4.772630672618385</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.085504922131839</v>
+        <v>1.048545242239566</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2781276746029317</v>
+        <v>-0.2724346218413279</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.791077330838909</v>
+        <v>2.794493162495871</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.822996805710353</v>
+        <v>-4.915396005441035</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.027479265742889</v>
+        <v>0.9905195858506162</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4208930074255821</v>
+        <v>-0.4151999546639783</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.704498607885429</v>
+        <v>2.707914439542391</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.760698806934231</v>
+        <v>-4.853098006664913</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.118734019050159</v>
+        <v>1.081774339157886</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4208930074255821</v>
+        <v>-0.4151999546639783</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.77083416168225</v>
+        <v>2.774249993339212</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.558908609269073</v>
+        <v>-4.651307808999755</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.90803097050562</v>
+        <v>0.8710712906133473</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2228748152564277</v>
+        <v>-0.2171817624948239</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.59822594937314</v>
+        <v>2.601641781030103</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.49901792762648</v>
+        <v>-4.591417127357162</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.002277475484833</v>
+        <v>0.9653177955925598</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1629841336138342</v>
+        <v>-0.1572910808522304</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.704450590680871</v>
+        <v>2.707866422337834</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.596758472251454</v>
+        <v>-4.689157671982136</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9778089937508865</v>
+        <v>0.9408493138586136</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1788734117468144</v>
+        <v>-0.1731803589852106</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.709544759917127</v>
+        <v>2.71296059157409</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.773096232374384</v>
+        <v>-4.865495432105066</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9058098705263864</v>
+        <v>0.8688501906341135</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3552111718697438</v>
+        <v>-0.34951811910814</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.602278084668041</v>
+        <v>2.605693916325003</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.77240686021316</v>
+        <v>-4.864806059943843</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9045772374308043</v>
+        <v>0.8676175575385314</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3552111718697438</v>
+        <v>-0.34951811910814</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.60076970270797</v>
+        <v>2.604185534364932</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.778977825267753</v>
+        <v>-4.871377024998435</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9018117188444035</v>
+        <v>0.8648520389521306</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3617821369243368</v>
+        <v>-0.3560890841627329</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.59668999111065</v>
+        <v>2.600105822767612</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.771023854972981</v>
+        <v>-4.863423054703663</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9049933069623122</v>
+        <v>0.8680336270700395</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3617821369243368</v>
+        <v>-0.3560890841627329</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.59668999111065</v>
+        <v>2.600105822767612</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.760650478639894</v>
+        <v>-4.853049678370576</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9155244145233516</v>
+        <v>0.8785647346310788</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3514087605912495</v>
+        <v>-0.3457157078296457</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.609295773938307</v>
+        <v>2.612711605595269</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.632966168845598</v>
+        <v>-4.72536536857628</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.971490511815795</v>
+        <v>0.9345308319235222</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.223724450796953</v>
+        <v>-0.2180313980353492</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.690798733189609</v>
+        <v>2.694214564846572</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.693632759247986</v>
+        <v>-4.786031958978668</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9339785481307117</v>
+        <v>0.897018868238439</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3054227675154867</v>
+        <v>-0.2997297147538829</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.628534415634362</v>
+        <v>2.631950247291324</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,19 +47108,19 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.509562338442501</v>
+        <v>3.509562338442499</v>
       </c>
       <c r="C1981" t="n">
         <v>2.658724842907396</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.693632759247986</v>
+        <v>-4.786031958978668</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9339785481307117</v>
+        <v>0.897018868238439</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3054227675154867</v>
+        <v>-0.2997297147538829</v>
       </c>
       <c r="G1981" t="n">
         <v>2.651788639893764</v>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226416</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913419</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024957</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.509562338442499</v>
+        <v>3.509562338442501</v>
       </c>
       <c r="C1981" t="n">
         <v>2.658724842907396</v>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-30.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.2%</t>
+          <t>-632.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.5%</t>
+          <t>-283.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.0%</t>
+          <t>-246.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.8%</t>
+          <t>-177.8%</t>
         </is>
       </c>
     </row>
@@ -47111,19 +47111,19 @@
         <v>3.509562338442501</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.658724842907396</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.786031958978668</v>
+        <v>-4.709139110508436</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.897018868238439</v>
+        <v>0.9318737102371606</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2997297147538829</v>
+        <v>-0.2228368662836505</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.651788639893764</v>
+        <v>2.682183658984092</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240531.xlsx
+++ b/tame_output/ON/bt/strategyON_20240531.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.5%</t>
+          <t>-631.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.0%</t>
+          <t>-282.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.3%</t>
+          <t>-245.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.8%</t>
+          <t>-177.1%</t>
         </is>
       </c>
     </row>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.59284502973804</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.076656222903914</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.723420488517018</v>
+        <v>-2.594466475300087</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526785920194838</v>
+        <v>1.604158328124997</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.64563118533836</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.096654895305488</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.819095975099415</v>
+        <v>-2.690141961882484</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.470496418083956</v>
+        <v>1.547868826014115</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-10.87766010507463</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.186772734570879</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.752154659070908</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.435982528400017</v>
+        <v>1.513354936330175</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-10.82564459110581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.161976193296952</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.752154659070908</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.439972864086418</v>
+        <v>1.517345272016576</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-10.96731643282993</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.220120156885342</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.752154659070908</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.438497637187676</v>
+        <v>1.515870045117835</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-10.9177255884051</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.185230408950536</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.831517827863005</v>
+        <v>-2.702563814646074</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.483305554007449</v>
+        <v>1.560677961937607</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.718573481168</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.118620699702379</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.666195301913191</v>
+        <v>-2.537241288696261</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.569447935930654</v>
+        <v>1.646820343860812</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.49272832844859</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.018703565578406</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.495314613109097</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.60418301431916</v>
+        <v>1.681555422249319</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.368149672111</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-0.9677329584873102</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.495314613109097</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.605322158875219</v>
+        <v>1.682694566805378</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.42104496015528</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-0.9862572995429177</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.490359267020651</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.610929140690395</v>
+        <v>1.688301548620553</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.13713622922653</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.8669601029327811</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.490359267020651</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.616662844929031</v>
+        <v>1.69403525285919</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.06576983661689</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.8481508082827878</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.418992874411003</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.649745418100955</v>
+        <v>1.727117826031113</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-9.801932969412817</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.7524995427140673</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.418992874411003</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.639861936788047</v>
+        <v>1.717234344718206</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.53469116854442</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.647437382866082</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.418992874411003</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.638027376288673</v>
+        <v>1.715399784218832</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.436784129867929</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.6085748823689463</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.479961137767377</v>
+        <v>-2.351007124550446</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.678518511231546</v>
+        <v>1.755890919161705</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.412830588891971</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.5983249598330698</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.45600759679142</v>
+        <v>-2.327053583574489</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.693559141962615</v>
+        <v>1.770931549892773</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.148770650569174</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.5059613006657031</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.062993645251693</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.83873478879454</v>
+        <v>1.916107196724699</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.441691027064337</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.2259164849240691</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.062993645251693</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.835947755134239</v>
+        <v>1.913320163064398</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.401506728698147</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.2094991416897516</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.151763360102433</v>
+        <v>-2.022809346885502</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.860401958041795</v>
+        <v>1.937774365971953</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.321436933160342</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.1781044022538727</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.071693564564629</v>
+        <v>-1.942739551347698</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.907810656585234</v>
+        <v>1.985183064515393</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.087955710930743</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.07678748452418072</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.838212342335031</v>
+        <v>-1.7092583291181</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.055823818760846</v>
+        <v>2.133196226691005</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-7.938289319923228</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.01981313843413357</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.745308851092495</v>
+        <v>-1.616354837875564</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.108673703193408</v>
+        <v>2.186046111123567</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-7.806013846292341</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>0.02846453776524793</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.613033377461608</v>
+        <v>-1.484079364244677</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.183406474118967</v>
+        <v>2.260778882049126</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.838729032049837</v>
+        <v>-7.615414171619189</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01819352414988629</v>
+        <v>0.1075194683221454</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.51679455000217</v>
+        <v>-1.293479689571524</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.243964831282267</v>
+        <v>2.377953747540654</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.589729233366256</v>
+        <v>-7.366414372935608</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1306997848469771</v>
+        <v>0.2200257290192367</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.51679455000217</v>
+        <v>-1.293479689571524</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.256871172505925</v>
+        <v>2.390860088764313</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.695319223139361</v>
+        <v>-7.472004362708712</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03951214066148312</v>
+        <v>0.04981380351077647</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.622384539775274</v>
+        <v>-1.399069679344628</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.065541249042844</v>
+        <v>2.199530165301232</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.714054125257958</v>
+        <v>-7.490739264827309</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.001538240368164523</v>
+        <v>0.09086418454042366</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.622384539775274</v>
+        <v>-1.399069679344628</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.114085590919931</v>
+        <v>2.248074507178318</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.566114083850358</v>
+        <v>-7.34279922341971</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05916466575696333</v>
+        <v>0.03016127841529581</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.602063623866717</v>
+        <v>-1.378748763436071</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.006399217776898</v>
+        <v>2.140388134035285</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.548955933719064</v>
+        <v>-7.325641073288415</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06101539195792416</v>
+        <v>0.02831055221433543</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.584905473735422</v>
+        <v>-1.361590613304777</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.007980121602196</v>
+        <v>2.141969037860584</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.505407526948374</v>
+        <v>-7.282092666517725</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05055664134474114</v>
+        <v>0.03876930282751845</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.584905473735422</v>
+        <v>-1.361590613304777</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.001019509507103</v>
+        <v>2.13500842576549</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.263259133494516</v>
+        <v>-7.039944273063867</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06076507041794521</v>
+        <v>0.1500910145902048</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.584905473735422</v>
+        <v>-1.361590613304777</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.015481863888246</v>
+        <v>2.149470780146634</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.154999996371994</v>
+        <v>-6.931685135941345</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09860084572614891</v>
+        <v>0.1879267898984085</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.584905473735422</v>
+        <v>-1.361590613304777</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.010013984347441</v>
+        <v>2.144002900605829</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.031708861554863</v>
+        <v>-6.808394001124214</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1454153936635785</v>
+        <v>0.2347413378358376</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.461614338918292</v>
+        <v>-1.238299478487646</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.081486759248296</v>
+        <v>2.215475675506684</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.01055966265142</v>
+        <v>-6.787244802220771</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1615760514622808</v>
+        <v>0.2509019956345404</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.440465140014848</v>
+        <v>-1.217150279584203</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.101877256827688</v>
+        <v>2.235866173086075</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.766794220667975</v>
+        <v>-6.543479360237327</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2548629366027093</v>
+        <v>0.3441888807749689</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.440465140014848</v>
+        <v>-1.217150279584203</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.097657965174738</v>
+        <v>2.231646881433126</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.619897192950106</v>
+        <v>-6.396582332519456</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3157460616098731</v>
+        <v>0.4050720057821331</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.39280689803626</v>
+        <v>-1.169492037605615</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.128377224281907</v>
+        <v>2.262366140540294</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.370046799001031</v>
+        <v>-6.146731938570381</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4084282941732051</v>
+        <v>0.4977542383454652</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.39280689803626</v>
+        <v>-1.169492037605615</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.121119299265609</v>
+        <v>2.255108215523996</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.194154706533599</v>
+        <v>-5.970839846102949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4823842546808268</v>
+        <v>0.5717101988530868</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.39280689803626</v>
+        <v>-1.169492037605615</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.124718422786258</v>
+        <v>2.258707339044645</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.022708243511135</v>
+        <v>-5.799393383080486</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5642903459443658</v>
+        <v>0.6536162901166258</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.221360435013797</v>
+        <v>-0.9980455745831515</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.240913806654289</v>
+        <v>2.374902722912677</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.797675243842312</v>
+        <v>-5.574360383411663</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6533240234281918</v>
+        <v>0.7426499676004519</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9963274353449744</v>
+        <v>-0.7730125749143286</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.37495408407188</v>
+        <v>2.508943000330267</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.734039501608378</v>
+        <v>-5.510724641177728</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6834731213760832</v>
+        <v>0.7727990655483428</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9326916931110398</v>
+        <v>-0.7093768326803941</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.417830330466558</v>
+        <v>2.551819246724945</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.64103946040248</v>
+        <v>-5.41772459997183</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7018673966422382</v>
+        <v>0.7911933408144978</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9326916931110398</v>
+        <v>-0.7093768326803941</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.399024589250354</v>
+        <v>2.533013505508741</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.40060896359762</v>
+        <v>-5.17729410316697</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7997826719890595</v>
+        <v>0.8891086161613195</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6922611963061795</v>
+        <v>-0.4689463358755338</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.545025963958147</v>
+        <v>2.679014880216535</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.328366395426425</v>
+        <v>-5.105051534995775</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8326090130923576</v>
+        <v>0.9219349572646176</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6922611963061795</v>
+        <v>-0.4689463358755338</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.548955277792967</v>
+        <v>2.682944194051355</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.275368073145037</v>
+        <v>-5.052053212714387</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8544869259222527</v>
+        <v>0.9438128700945128</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6369249373042407</v>
+        <v>-0.413610076873595</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.582835617111471</v>
+        <v>2.716824533369858</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.16656318766531</v>
+        <v>-4.94324832723466</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8950069513341372</v>
+        <v>0.9843328955063968</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6369249373042407</v>
+        <v>-0.413610076873595</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.579833688331464</v>
+        <v>2.713822604589851</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.946542389628299</v>
+        <v>-4.72322752919765</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9845943075595553</v>
+        <v>1.073920251731815</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4957050922362605</v>
+        <v>-0.2723902318056147</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.666144632382867</v>
+        <v>2.800133548641254</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.813674700565022</v>
+        <v>-4.590359840134372</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.05363556598669</v>
+        <v>1.14296151015895</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4957050922362605</v>
+        <v>-0.2723902318056147</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.68203881518469</v>
+        <v>2.816027731443077</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.654159597045652</v>
+        <v>-4.430844736615002</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.11858745183474</v>
+        <v>1.207913396006999</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3361899887168905</v>
+        <v>-0.1128751282862448</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.778893721736614</v>
+        <v>2.912882637995001</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.509487451945914</v>
+        <v>-4.286172591515265</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.186544412436074</v>
+        <v>1.275870356608334</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1915178436171531</v>
+        <v>0.03179701681349262</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.875785111357896</v>
+        <v>3.009774027616283</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.569362279303607</v>
+        <v>-4.346047418872957</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.148631972894423</v>
+        <v>1.237957917066683</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2513926709748452</v>
+        <v>-0.0280778105441995</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.825897706344707</v>
+        <v>2.959886622603094</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.482562781524598</v>
+        <v>-4.259247921093948</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.205752265328593</v>
+        <v>1.295078209500853</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2513926709748452</v>
+        <v>-0.0280778105441995</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.848298199667273</v>
+        <v>2.98228711592566</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.485032487986404</v>
+        <v>-4.261717627555754</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.204836784117283</v>
+        <v>1.294162728289543</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2538623774366514</v>
+        <v>-0.03054751700600566</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.846888777163601</v>
+        <v>2.980877693421988</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.553402674310414</v>
+        <v>-4.330087813879764</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.188495632062381</v>
+        <v>1.277821576234641</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2445866784004365</v>
+        <v>-0.02127181796979072</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.863461119060032</v>
+        <v>2.997450035318419</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.661940855226548</v>
+        <v>-4.438625994795898</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.135517068327818</v>
+        <v>1.224843012500078</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2445866784004365</v>
+        <v>-0.02127181796979072</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.853897827691923</v>
+        <v>2.987886743950311</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.692934014555253</v>
+        <v>-4.469619154124604</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.947829369636723</v>
+        <v>1.037155313808983</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2445866784004365</v>
+        <v>-0.02127181796979072</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.67860739273231</v>
+        <v>2.812596308990698</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.517459754762784</v>
+        <v>-4.294144894332135</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.022586305545498</v>
+        <v>1.111912249717758</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2445866784004365</v>
+        <v>-0.02127181796979072</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.683174624724098</v>
+        <v>2.817163540982485</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.628396007404033</v>
+        <v>-4.405081146973384</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.953953833250206</v>
+        <v>1.043279777422466</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2445866784004365</v>
+        <v>-0.02127181796979072</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.658916653485305</v>
+        <v>2.792905569743692</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.831422584947267</v>
+        <v>-4.608107724516617</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8758745874528182</v>
+        <v>0.965200531625078</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4476132559436699</v>
+        <v>-0.2242983955130241</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.54023209217927</v>
+        <v>2.674221008437658</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.673496986011973</v>
+        <v>-4.450182125581324</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9492172134590677</v>
+        <v>1.038543157631328</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4476132559436699</v>
+        <v>-0.2242983955130241</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.550404478611403</v>
+        <v>2.68439339486979</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.587253522985596</v>
+        <v>-4.363938662554946</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9786608692434791</v>
+        <v>1.067986813415739</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4476132559436699</v>
+        <v>-0.2242983955130241</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.545350749185263</v>
+        <v>2.679339665443651</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.632560342384576</v>
+        <v>-4.409245481953926</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9523139169284127</v>
+        <v>1.041639861100673</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4884234189529006</v>
+        <v>-0.2651085585222549</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.51264042682425</v>
+        <v>2.646629343082638</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.661593447086877</v>
+        <v>-4.438278586656227</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9412525480805938</v>
+        <v>1.030578492252854</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4884234189529006</v>
+        <v>-0.2651085585222549</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.513192299857351</v>
+        <v>2.647181216115739</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.568782965636017</v>
+        <v>-4.345468105205367</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9076494325523035</v>
+        <v>0.9969753767245633</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3956129375020413</v>
+        <v>-0.1722980770713956</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.498151280619233</v>
+        <v>2.632140196877621</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.520219913414987</v>
+        <v>-4.296905052984338</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9289481293653161</v>
+        <v>1.018274073537576</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3470498852810111</v>
+        <v>-0.1237350248503654</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.529162587876452</v>
+        <v>2.663151504134839</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.407548695178737</v>
+        <v>-4.184233834748087</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9690923251715393</v>
+        <v>1.058418269343799</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2343786670447609</v>
+        <v>-0.01106380661411516</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.591841027329925</v>
+        <v>2.725829943588312</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.295171693996064</v>
+        <v>-4.071856833565414</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.019534421475276</v>
+        <v>1.108860365647536</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2343786670447609</v>
+        <v>-0.01106380661411516</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.597332323160592</v>
+        <v>2.73132123941898</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.493406262882795</v>
+        <v>-4.270091402452145</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9517377956891224</v>
+        <v>1.041063739861382</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4326132359314915</v>
+        <v>-0.2092983755008457</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.489888783597093</v>
+        <v>2.62387769985548</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.576407543908074</v>
+        <v>-4.353092683477424</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7568930032796641</v>
+        <v>0.8462189474519239</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4511841204586652</v>
+        <v>-0.2278692600280195</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.317101972881442</v>
+        <v>2.45109088913983</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.703474550215062</v>
+        <v>-4.480159689784412</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8262158614760744</v>
+        <v>0.9155418056483344</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4511841204586652</v>
+        <v>-0.2278692600280195</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.437251633600648</v>
+        <v>2.571240549859035</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.790073133196165</v>
+        <v>-4.566758272765515</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8060894543859562</v>
+        <v>0.8954153985582161</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4511841204586652</v>
+        <v>-0.2278692600280195</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.451764659702971</v>
+        <v>2.585753575961358</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.751689470638014</v>
+        <v>-4.528374610207364</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8188623607515855</v>
+        <v>0.9081883049238453</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4128004579005141</v>
+        <v>-0.1894855974698683</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.47221429858023</v>
+        <v>2.606203214838617</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.574573140602848</v>
+        <v>-4.351258280172198</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8864379216109537</v>
+        <v>0.9757638657832137</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4128004579005141</v>
+        <v>-0.1894855974698683</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.468943327425532</v>
+        <v>2.602932243683919</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.544871016626554</v>
+        <v>-4.321556156195904</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8990021629633844</v>
+        <v>0.9883281071356442</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4172705831158274</v>
+        <v>-0.1939557226851817</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.466944644058257</v>
+        <v>2.600933560316645</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.365495595387786</v>
+        <v>-4.142180734957137</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9645393067653059</v>
+        <v>1.053865250937566</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2604938249451088</v>
+        <v>-0.03717896451446301</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.554797674267102</v>
+        <v>2.68878659052549</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.410509808908392</v>
+        <v>-4.187194948477742</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9273410766886532</v>
+        <v>1.016667020860913</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2908427202597134</v>
+        <v>-0.06752785982906762</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.51739579240993</v>
+        <v>2.651384708668317</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.677514319180827</v>
+        <v>-4.454199458750177</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8262308349186249</v>
+        <v>0.9155567790908847</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4852057583026619</v>
+        <v>-0.2618908978720162</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.406469531923106</v>
+        <v>2.540458448181494</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.778712100618</v>
+        <v>-4.55539724018735</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7849556442402572</v>
+        <v>0.8742815884125172</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5536145718479811</v>
+        <v>-0.3302997114173354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.364628165692416</v>
+        <v>2.498617081950803</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.746236514447228</v>
+        <v>-4.522921654016578</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.795545840262883</v>
+        <v>0.8848717844351428</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5536145718479811</v>
+        <v>-0.3302997114173354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.362228127246733</v>
+        <v>2.49621704350512</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.72719838673993</v>
+        <v>-4.503883526309281</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7996858105540467</v>
+        <v>0.8890117547263066</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6117981831791757</v>
+        <v>-0.3884833227485299</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.323842679656261</v>
+        <v>2.457831595914648</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.758325017890549</v>
+        <v>-4.535010157459899</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9648170270324798</v>
+        <v>1.05414297120474</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6117981831791757</v>
+        <v>-0.3884833227485299</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.501424548594942</v>
+        <v>2.635413464853329</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.81064539849134</v>
+        <v>-4.587330538060691</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9447222037782967</v>
+        <v>1.034048147950557</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5768513231703035</v>
+        <v>-0.3535364627396578</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.523225993586399</v>
+        <v>2.657214909844786</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.954968304416259</v>
+        <v>-4.73165344398561</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8930015718052551</v>
+        <v>0.9823275159775151</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5768513231703035</v>
+        <v>-0.3535364627396578</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.529234523983324</v>
+        <v>2.663223440241712</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.807225334181257</v>
+        <v>-4.583910473750607</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.031251407691278</v>
+        <v>1.120577351863538</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4090439659354204</v>
+        <v>-0.1857291055047746</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.709071586116276</v>
+        <v>2.843060502374664</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.909240016712478</v>
+        <v>-4.685925156281828</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9932391562102705</v>
+        <v>1.082565100382531</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4090439659354204</v>
+        <v>-0.1857291055047746</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.711865207647757</v>
+        <v>2.845854123906145</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.772630672618385</v>
+        <v>-4.549315812187736</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.048545242239566</v>
+        <v>1.137871186411826</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2724346218413279</v>
+        <v>-0.04911976141068214</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.794493162495871</v>
+        <v>2.928482078754258</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.915396005441035</v>
+        <v>-4.692081145010386</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9905195858506162</v>
+        <v>1.079845530022876</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4151999546639783</v>
+        <v>-0.1918850942333326</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.707914439542391</v>
+        <v>2.841903355800778</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.853098006664913</v>
+        <v>-4.629783146234264</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.081774339157886</v>
+        <v>1.171100283330146</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4151999546639783</v>
+        <v>-0.1918850942333326</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.774249993339212</v>
+        <v>2.908238909597599</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.651307808999755</v>
+        <v>-4.427992948569106</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8710712906133473</v>
+        <v>0.9603972347856071</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2171817624948239</v>
+        <v>0.006133097935821841</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.601641781030103</v>
+        <v>2.73563069728849</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.591417127357162</v>
+        <v>-4.368102266926512</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9653177955925598</v>
+        <v>1.05464373976482</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1572910808522304</v>
+        <v>0.06602377957841532</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.707866422337834</v>
+        <v>2.841855338596221</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.689157671982136</v>
+        <v>-4.465842811551487</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9408493138586136</v>
+        <v>1.030175258030873</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1731803589852106</v>
+        <v>0.05013450144543513</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.71296059157409</v>
+        <v>2.846949507832477</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.865495432105066</v>
+        <v>-4.642180571674416</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8688501906341135</v>
+        <v>0.9581761348063735</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.34951811910814</v>
+        <v>-0.1262032586774943</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.605693916325003</v>
+        <v>2.739682832583391</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.864806059943843</v>
+        <v>-4.641491199513193</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8676175575385314</v>
+        <v>0.9569435017107912</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.34951811910814</v>
+        <v>-0.1262032586774943</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.604185534364932</v>
+        <v>2.738174450623319</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.871377024998435</v>
+        <v>-4.648062164567786</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8648520389521306</v>
+        <v>0.9541779831243904</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3560890841627329</v>
+        <v>-0.1327742237320872</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.600105822767612</v>
+        <v>2.734094739026</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.863423054703663</v>
+        <v>-4.640108194273013</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8680336270700395</v>
+        <v>0.9573595712422993</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3560890841627329</v>
+        <v>-0.1327742237320872</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.600105822767612</v>
+        <v>2.734094739026</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.853049678370576</v>
+        <v>-4.629734817939926</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8785647346310788</v>
+        <v>0.9678906788033386</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3457157078296457</v>
+        <v>-0.1224008473989999</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.612711605595269</v>
+        <v>2.746700521853657</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.72536536857628</v>
+        <v>-4.50205050814563</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9345308319235222</v>
+        <v>1.023856776095782</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2180313980353492</v>
+        <v>0.005283462395296534</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.694214564846572</v>
+        <v>2.82820348110496</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.786031958978668</v>
+        <v>-4.562717098548019</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.897018868238439</v>
+        <v>0.9863448124106988</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2997297147538829</v>
+        <v>-0.07641485432323714</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.631950247291324</v>
+        <v>2.765939163549711</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.509562338442501</v>
+        <v>3.848450869854035</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.709139110508436</v>
+        <v>-4.697043549914061</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9318737102371606</v>
+        <v>0.9367119344749106</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2228368662836505</v>
+        <v>-0.2107413056892795</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.682183658984092</v>
+        <v>2.689440995340715</v>
       </c>
     </row>
   </sheetData>
